--- a/public/downloads/ZhaoTrends2019.xlsx
+++ b/public/downloads/ZhaoTrends2019.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>O</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
+    <t>HO</t>
   </si>
   <si>
     <t>HO2</t>
   </si>
   <si>
-    <t>HO</t>
+    <t>O</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>129</v>
       </c>
       <c r="N3" s="5">
-        <v>6101.212398290634</v>
+        <v>6101212.398290634</v>
       </c>
       <c r="O3" s="4">
-        <v>0.1612498982025698</v>
+        <v>161.2498982025698</v>
       </c>
       <c r="P3" s="5">
         <v>37837</v>
@@ -709,10 +732,10 @@
         <v>129</v>
       </c>
       <c r="N4" s="5">
-        <v>3409.641594171524</v>
+        <v>3409641.594171524</v>
       </c>
       <c r="O4" s="4">
-        <v>0.1097512342412053</v>
+        <v>109.7512342412053</v>
       </c>
       <c r="P4" s="5">
         <v>31067</v>
@@ -759,10 +782,10 @@
         <v>129</v>
       </c>
       <c r="N5" s="5">
-        <v>4764.663021087646</v>
+        <v>4764663.021087646</v>
       </c>
       <c r="O5" s="4">
-        <v>0.136304583507485</v>
+        <v>136.304583507485</v>
       </c>
       <c r="P5" s="5">
         <v>34956</v>
@@ -809,10 +832,10 @@
         <v>129</v>
       </c>
       <c r="N6" s="5">
-        <v>3777.457894086838</v>
+        <v>3777457.894086838</v>
       </c>
       <c r="O6" s="4">
-        <v>0.1014382205238282</v>
+        <v>101.4382205238282</v>
       </c>
       <c r="P6" s="5">
         <v>37239</v>
@@ -859,10 +882,10 @@
         <v>129</v>
       </c>
       <c r="N7" s="5">
-        <v>3603.115580558777</v>
+        <v>3603115.580558777</v>
       </c>
       <c r="O7" s="4">
-        <v>0.1263320213372174</v>
+        <v>126.3320213372174</v>
       </c>
       <c r="P7" s="5">
         <v>28521</v>
@@ -909,10 +932,10 @@
         <v>129</v>
       </c>
       <c r="N8" s="5">
-        <v>1989.440925359726</v>
+        <v>1989440.925359726</v>
       </c>
       <c r="O8" s="4">
-        <v>0.04421078080312286</v>
+        <v>44.21078080312287</v>
       </c>
       <c r="P8" s="5">
         <v>44999</v>
@@ -959,10 +982,10 @@
         <v>129</v>
       </c>
       <c r="N9" s="5">
-        <v>2097.360929965973</v>
+        <v>2097360.929965973</v>
       </c>
       <c r="O9" s="4">
-        <v>0.06063313954398464</v>
+        <v>60.63313954398465</v>
       </c>
       <c r="P9" s="5">
         <v>34591</v>
@@ -1009,10 +1032,10 @@
         <v>129</v>
       </c>
       <c r="N10" s="5">
-        <v>2704.046774864197</v>
+        <v>2704046.774864197</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08153806274656084</v>
+        <v>81.53806274656084</v>
       </c>
       <c r="P10" s="5">
         <v>33163</v>
@@ -1059,10 +1082,10 @@
         <v>129</v>
       </c>
       <c r="N11" s="5">
-        <v>2302.424530982971</v>
+        <v>2302424.530982971</v>
       </c>
       <c r="O11" s="4">
-        <v>0.0656335385114872</v>
+        <v>65.6335385114872</v>
       </c>
       <c r="P11" s="5">
         <v>35080</v>
@@ -1109,10 +1132,10 @@
         <v>129</v>
       </c>
       <c r="N12" s="5">
-        <v>1716.708913564682</v>
+        <v>1716708.913564682</v>
       </c>
       <c r="O12" s="4">
-        <v>0.05375802948470852</v>
+        <v>53.75802948470852</v>
       </c>
       <c r="P12" s="5">
         <v>31934</v>
@@ -1159,10 +1182,10 @@
         <v>129</v>
       </c>
       <c r="N13" s="5">
-        <v>2979.309820890427</v>
+        <v>2979309.820890427</v>
       </c>
       <c r="O13" s="4">
-        <v>0.09108532272128242</v>
+        <v>91.08532272128242</v>
       </c>
       <c r="P13" s="5">
         <v>32709</v>
@@ -1209,10 +1232,10 @@
         <v>129</v>
       </c>
       <c r="N14" s="5">
-        <v>6222.585938215256</v>
+        <v>6222585.938215256</v>
       </c>
       <c r="O14" s="4">
-        <v>0.1629333072769829</v>
+        <v>162.9333072769829</v>
       </c>
       <c r="P14" s="5">
         <v>38191</v>
@@ -1259,10 +1282,10 @@
         <v>129</v>
       </c>
       <c r="N15" s="5">
-        <v>4813.38399720192</v>
+        <v>4813383.99720192</v>
       </c>
       <c r="O15" s="4">
-        <v>0.1582100971996424</v>
+        <v>158.2100971996424</v>
       </c>
       <c r="P15" s="5">
         <v>30424</v>
@@ -1309,10 +1332,10 @@
         <v>129</v>
       </c>
       <c r="N16" s="5">
-        <v>3741.749072313309</v>
+        <v>3741749.072313309</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09616667280868973</v>
+        <v>96.16667280868974</v>
       </c>
       <c r="P16" s="5">
         <v>38909</v>
@@ -1359,10 +1382,10 @@
         <v>129</v>
       </c>
       <c r="N17" s="5">
-        <v>2916.418608427048</v>
+        <v>2916418.608427048</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09547941098140605</v>
+        <v>95.47941098140605</v>
       </c>
       <c r="P17" s="5">
         <v>30545</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,132 +1497,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4814411625273246</v>
+        <v>0.292102739629906</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4345382506049433</v>
+        <v>0.3908821397642154</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4121510014596707</v>
+        <v>0.2890956717140729</v>
       </c>
       <c r="E3" s="4">
-        <v>66.58202816010117</v>
+        <v>60.92627748773928</v>
       </c>
       <c r="F3" s="4">
-        <v>45.42037354976332</v>
+        <v>45.86884137141673</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J3" s="5">
         <v>34</v>
       </c>
       <c r="K3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1450406291715316</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2794777826185646</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3425352633737049</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5183448911400939</v>
+        <v>0.5547565316069867</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4321524507079449</v>
+        <v>0.8949635681421841</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2389144674736325</v>
+        <v>0.4531663027832727</v>
       </c>
       <c r="E4" s="4">
-        <v>63.60781521911117</v>
+        <v>52.75905711121656</v>
       </c>
       <c r="F4" s="4">
-        <v>42.14687061026996</v>
+        <v>37.02148691535317</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K4" s="5">
         <v>1</v>
       </c>
       <c r="L4" s="5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5547565316069867</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.8949635681421841</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2410538389240517</v>
+        <v>0.5721147109115193</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3078267364102338</v>
+        <v>0.3242602003402109</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2231591905796534</v>
+        <v>0.4483244709959745</v>
       </c>
       <c r="E5" s="4">
-        <v>67.43078626799556</v>
+        <v>60.389969941465</v>
       </c>
       <c r="F5" s="4">
-        <v>45.14541387024645</v>
+        <v>45.90239841839654</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>36</v>
+      </c>
+      <c r="K5" s="5">
         <v>1</v>
       </c>
-      <c r="J5" s="5">
-        <v>33</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
       <c r="L5" s="5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.06084108905621864</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5620878266175199</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3155686161893225</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1703,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1722,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1764,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1795,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5213087472313306</v>
+        <v>0.339294041953577</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3103228896830623</v>
+        <v>0.430256443639323</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4256565981370922</v>
+        <v>0.3440092019272478</v>
       </c>
       <c r="E3" s="4">
-        <v>66.37636449928803</v>
+        <v>60.88593576965651</v>
       </c>
       <c r="F3" s="4">
-        <v>46.52879662868754</v>
+        <v>46.0779876177103</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.188366275010848</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2550584957226067</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3881023212186598</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6301652913091615</v>
+        <v>0.7782171289934602</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3920189298486487</v>
+        <v>0.9780721101025358</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3765861953675509</v>
+        <v>0.6889103028071557</v>
       </c>
       <c r="E4" s="4">
-        <v>57.6585983230499</v>
+        <v>52.3959816484734</v>
       </c>
       <c r="F4" s="4">
-        <v>39.0622236095931</v>
+        <v>37.2321939545289</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
       </c>
       <c r="H4" s="5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" s="5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7782171289934602</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.9780721101025358</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2268108604929364</v>
+        <v>0.4410084259152415</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2127604994531283</v>
+        <v>0.4882703869118896</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2255076081027718</v>
+        <v>0.4444978815921085</v>
       </c>
       <c r="E5" s="4">
-        <v>68.16010124980212</v>
+        <v>60.96899224806192</v>
       </c>
       <c r="F5" s="4">
-        <v>49.27084959159248</v>
+        <v>46.05665678164555</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3169623921071971</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3762611849704252</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.341423480367481</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2001,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2020,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2062,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,25 +2093,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3513032888831712</v>
+        <v>0.2410538389240517</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2262756714511498</v>
+        <v>0.3078267364102338</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3186825540136428</v>
+        <v>0.2231591905796534</v>
       </c>
       <c r="E3" s="4">
-        <v>67.44186046511629</v>
+        <v>67.43078626799556</v>
       </c>
       <c r="F3" s="4">
-        <v>46.55663076843022</v>
+        <v>45.14541387024645</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
@@ -1913,13 +2138,13 @@
         <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>33</v>
@@ -1927,91 +2152,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1433422166278205</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.265876745256695</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2726549939204798</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5337643651623405</v>
+        <v>0.5183448911400939</v>
       </c>
       <c r="C4" s="4">
-        <v>0.296849615691005</v>
+        <v>0.4321524507079449</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1653990429371151</v>
+        <v>0.2389144674736325</v>
       </c>
       <c r="E4" s="4">
-        <v>60.70479354532522</v>
+        <v>63.60781521911117</v>
       </c>
       <c r="F4" s="4">
-        <v>40.09676915873254</v>
+        <v>42.14687061026996</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
       </c>
       <c r="H4" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
+        <v>34</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
         <v>33</v>
       </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
-      <c r="L4" s="5">
-        <v>31</v>
-      </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4321524507079449</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6391539010962983</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1266158835306562</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2011092982621592</v>
+        <v>0.4814411625273246</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2440251503466833</v>
+        <v>0.4345382506049433</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1748760195511653</v>
+        <v>0.4121510014596707</v>
       </c>
       <c r="E5" s="4">
-        <v>67.65068818224962</v>
+        <v>66.58202816010117</v>
       </c>
       <c r="F5" s="4">
-        <v>46.86176577701472</v>
+        <v>45.42037354976332</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2417865930804247</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4900874771249432</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2485350488582984</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2301,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2309,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2320,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2362,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2393,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4757977361344878</v>
+        <v>0.2268108604929364</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3430659039495936</v>
+        <v>0.2127604994531283</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3598418816669392</v>
+        <v>0.2255076081027718</v>
       </c>
       <c r="E3" s="4">
-        <v>60.96582819174174</v>
+        <v>68.16010124980212</v>
       </c>
       <c r="F3" s="4">
-        <v>37.99620207065203</v>
+        <v>49.27084959159248</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.04631235105259433</v>
+      </c>
+      <c r="O3" s="5">
+        <v>14</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2259408207373873</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2210198118478979</v>
+      </c>
+      <c r="R3" s="5">
+        <v>14</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4977590126208414</v>
+        <v>0.6301652913091615</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2263647330938738</v>
+        <v>0.3920189298486487</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2725917156945118</v>
+        <v>0.3765861953675509</v>
       </c>
       <c r="E4" s="4">
-        <v>56.78136370827416</v>
+        <v>57.6585983230499</v>
       </c>
       <c r="F4" s="4">
-        <v>35.38161385984088</v>
+        <v>39.0622236095931</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
       </c>
       <c r="H4" s="5">
+        <v>6</v>
+      </c>
+      <c r="I4" s="5">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5">
+        <v>31</v>
+      </c>
+      <c r="K4" s="5">
         <v>3</v>
       </c>
-      <c r="I4" s="5">
-        <v>2</v>
-      </c>
-      <c r="J4" s="5">
-        <v>38</v>
-      </c>
-      <c r="K4" s="5">
-        <v>2</v>
-      </c>
       <c r="L4" s="5">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.3920189298486487</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7101069127993289</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2442850955143073</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.281540273394708</v>
+        <v>0.5213087472313306</v>
       </c>
       <c r="C5" s="4">
-        <v>0.426567500303148</v>
+        <v>0.3103228896830623</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2635863335904176</v>
+        <v>0.4256565981370922</v>
       </c>
       <c r="E5" s="4">
-        <v>62.72187944945409</v>
+        <v>66.37636449928803</v>
       </c>
       <c r="F5" s="4">
-        <v>40.38343478487111</v>
+        <v>46.52879662868754</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.05533725346857198</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.515432763837167</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2952309114643608</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2601,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2609,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2620,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2662,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,66 +2693,102 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.688300756281058</v>
+        <v>0.2011092982621592</v>
       </c>
       <c r="C3" s="4">
-        <v>1.309690255425153</v>
+        <v>0.2440251503466833</v>
       </c>
       <c r="D3" s="4">
-        <v>1.591564660821516</v>
+        <v>0.1748760195511653</v>
       </c>
       <c r="E3" s="4">
-        <v>39.31419079259607</v>
+        <v>67.65068818224962</v>
       </c>
       <c r="F3" s="4">
-        <v>41.2598199885544</v>
+        <v>46.86176577701472</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>35</v>
       </c>
       <c r="M3" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.007506069033812679</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2029826499919381</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2440251503466833</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.160471146272059</v>
+        <v>0.5337643651623405</v>
       </c>
       <c r="C4" s="4">
-        <v>0.8527967721204854</v>
+        <v>0.296849615691005</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5659549594898504</v>
+        <v>0.1653990429371151</v>
       </c>
       <c r="E4" s="4">
-        <v>38.69799082423673</v>
+        <v>60.70479354532522</v>
       </c>
       <c r="F4" s="4">
-        <v>39.50444825971575</v>
+        <v>40.09676915873254</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
@@ -2380,64 +2797,100 @@
         <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.264519301921657</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6573473334014234</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2471088495615334</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8581807662624207</v>
+        <v>0.3513032888831712</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7641834990447945</v>
+        <v>0.2262756714511498</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7591090060133976</v>
+        <v>0.3186825540136428</v>
       </c>
       <c r="E5" s="4">
-        <v>39.89795918367354</v>
+        <v>67.44186046511629</v>
       </c>
       <c r="F5" s="4">
-        <v>42.48322147651007</v>
+        <v>46.55663076843022</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>34</v>
+      </c>
+      <c r="K5" s="5">
         <v>1</v>
       </c>
-      <c r="J5" s="5">
-        <v>35</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
       <c r="L5" s="5">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.01602553771226035</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3486944804183846</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2280562867525121</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2901,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2909,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2920,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2962,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2993,200 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.441815090203354</v>
+        <v>0.281540273394708</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3558026887401708</v>
+        <v>0.426567500303148</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3731311501397089</v>
+        <v>0.2635863335904176</v>
       </c>
       <c r="E3" s="4">
-        <v>66.61841480778359</v>
+        <v>62.72187944945409</v>
       </c>
       <c r="F3" s="4">
-        <v>42.42209042193451</v>
+        <v>40.38343478487111</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3109015127577782</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2554718453357407</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2580370198730459</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5693315082241729</v>
+        <v>0.4977590126208414</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2797902151156889</v>
+        <v>0.2263647330938738</v>
       </c>
       <c r="D4" s="4">
-        <v>0.455115756415648</v>
+        <v>0.2725917156945118</v>
       </c>
       <c r="E4" s="4">
-        <v>65.52523334915404</v>
+        <v>56.78136370827416</v>
       </c>
       <c r="F4" s="4">
-        <v>41.31730919307006</v>
+        <v>35.38161385984088</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4977590126208414</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2263647330938738</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3895111775843352</v>
+        <v>0.4757977361344878</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3729718360686863</v>
+        <v>0.3430659039495936</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3874703929867783</v>
+        <v>0.3598418816669392</v>
       </c>
       <c r="E5" s="4">
-        <v>67.54152823920268</v>
+        <v>60.96582819174174</v>
       </c>
       <c r="F5" s="4">
-        <v>42.88200405806156</v>
+        <v>37.99620207065203</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>4</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4757977361344878</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3430659039495936</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3197,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3205,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3216,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3258,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3289,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.650440575139813</v>
+        <v>0.8581807662624207</v>
       </c>
       <c r="C3" s="4">
-        <v>1.267197945710052</v>
+        <v>0.7641834990447945</v>
       </c>
       <c r="D3" s="4">
-        <v>1.612829974890428</v>
+        <v>0.7591090060133976</v>
       </c>
       <c r="E3" s="4">
-        <v>41.82882455307691</v>
+        <v>39.89795918367354</v>
       </c>
       <c r="F3" s="4">
-        <v>43.7651526975701</v>
+        <v>42.48322147651007</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M3" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.4025804568760946</v>
+      </c>
+      <c r="O3" s="5">
+        <v>7</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6266590708685068</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6273793087082586</v>
+      </c>
+      <c r="R3" s="5">
+        <v>7</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>1.062508143136176</v>
+        <v>1.160471146272059</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6700573249726255</v>
+        <v>0.8527967721204854</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6267034674126268</v>
+        <v>0.5659549594898504</v>
       </c>
       <c r="E4" s="4">
-        <v>41.55276063913941</v>
+        <v>38.69799082423673</v>
       </c>
       <c r="F4" s="4">
-        <v>40.71744446178633</v>
+        <v>39.50444825971575</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
       </c>
       <c r="H4" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.03839443161191663</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.181007702715642</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.847311853318783</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7320536526996768</v>
+        <v>1.688300756281058</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7799301286153022</v>
+        <v>1.309690255425153</v>
       </c>
       <c r="D5" s="4">
-        <v>0.7609431386570387</v>
+        <v>1.591564660821516</v>
       </c>
       <c r="E5" s="4">
-        <v>43.2162632494857</v>
+        <v>39.31419079259607</v>
       </c>
       <c r="F5" s="4">
-        <v>45.00702356797252</v>
+        <v>41.2598199885544</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-1.464623612093163</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8951663319147173</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.6581558553898433</v>
+      </c>
+      <c r="R5" s="5">
+        <v>4</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3497,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3505,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3516,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3558,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,40 +3589,58 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3793902071943199</v>
+        <v>0.3895111775843352</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2903745817735168</v>
+        <v>0.3729718360686863</v>
       </c>
       <c r="D3" s="4">
-        <v>0.332009425911453</v>
+        <v>0.3874703929867783</v>
       </c>
       <c r="E3" s="4">
-        <v>64.35927859515901</v>
+        <v>67.54152823920268</v>
       </c>
       <c r="F3" s="4">
-        <v>40.81473388481338</v>
+        <v>42.88200405806156</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
         <v>33</v>
@@ -2992,25 +3648,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2453656339305791</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2204809633128243</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2541752771055424</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4719288526607744</v>
+        <v>0.5693315082241729</v>
       </c>
       <c r="C4" s="4">
-        <v>0.291085385273112</v>
+        <v>0.2797902151156889</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2188991384474744</v>
+        <v>0.455115756415648</v>
       </c>
       <c r="E4" s="4">
-        <v>61.29014396456257</v>
+        <v>65.52523334915404</v>
       </c>
       <c r="F4" s="4">
-        <v>37.94131418760741</v>
+        <v>41.31730919307006</v>
       </c>
       <c r="G4" s="5">
         <v>43</v>
@@ -3033,25 +3707,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1272178452830015</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4696097253795317</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2373842666880218</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2544112974774244</v>
+        <v>0.441815090203354</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3025212138836768</v>
+        <v>0.3558026887401708</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2383272885119961</v>
+        <v>0.3731311501397089</v>
       </c>
       <c r="E5" s="4">
-        <v>65.18905236513214</v>
+        <v>66.61841480778359</v>
       </c>
       <c r="F5" s="4">
-        <v>41.2707455387341</v>
+        <v>42.42209042193451</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
@@ -3074,9 +3766,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1068164233666424</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.389147808070101</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3400651850732983</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3797,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.7320536526996768</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.7799301286153022</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.7609431386570387</v>
+      </c>
+      <c r="E3" s="4">
+        <v>43.2162632494857</v>
+      </c>
+      <c r="F3" s="4">
+        <v>45.00702356797252</v>
+      </c>
+      <c r="G3" s="5">
+        <v>43</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>33</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>33</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.232779971657087</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6054024404024686</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7540656873200703</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1.062508143136176</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.6700573249726255</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6267034674126268</v>
+      </c>
+      <c r="E4" s="4">
+        <v>41.55276063913941</v>
+      </c>
+      <c r="F4" s="4">
+        <v>40.71744446178633</v>
+      </c>
+      <c r="G4" s="5">
+        <v>43</v>
+      </c>
+      <c r="H4" s="5">
+        <v>8</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>34</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>33</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1282149714834951</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>1.127787548235959</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6843698272397872</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1.650440575139813</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1.267197945710052</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1.612829974890428</v>
+      </c>
+      <c r="E5" s="4">
+        <v>41.82882455307691</v>
+      </c>
+      <c r="F5" s="4">
+        <v>43.7651526975701</v>
+      </c>
+      <c r="G5" s="5">
+        <v>43</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>40</v>
+      </c>
+      <c r="K5" s="5">
+        <v>4</v>
+      </c>
+      <c r="L5" s="5">
+        <v>33</v>
+      </c>
+      <c r="M5" s="5">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-1.485050212914359</v>
+      </c>
+      <c r="O5" s="5">
+        <v>6</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8204871507524281</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4673148604343169</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2544112974774244</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3025212138836768</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2383272885119961</v>
+      </c>
+      <c r="E3" s="4">
+        <v>65.18905236513214</v>
+      </c>
+      <c r="F3" s="4">
+        <v>41.2707455387341</v>
+      </c>
+      <c r="G3" s="5">
+        <v>43</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>33</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>33</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1050346411140037</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2198017569366305</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3025212138836768</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4719288526607744</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.291085385273112</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.2188991384474744</v>
+      </c>
+      <c r="E4" s="4">
+        <v>61.29014396456257</v>
+      </c>
+      <c r="F4" s="4">
+        <v>37.94131418760741</v>
+      </c>
+      <c r="G4" s="5">
+        <v>43</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>34</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>34</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1797096455886912</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.605475944604511</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3329217843935517</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3793902071943199</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2903745817735168</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.332009425911453</v>
+      </c>
+      <c r="E5" s="4">
+        <v>64.35927859515901</v>
+      </c>
+      <c r="F5" s="4">
+        <v>40.81473388481338</v>
+      </c>
+      <c r="G5" s="5">
+        <v>43</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>34</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>33</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.1470072226634819</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3465128776009282</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2634717998006036</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>14.72868217054264</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5.426356589147287</v>
+      </c>
+      <c r="D3" s="3">
+        <v>79.84496124031007</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="F3" s="3">
+        <v>79.06976744186046</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4976887155806461</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3196827724274477</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.4010734255587064</v>
+      </c>
+      <c r="K3" s="4">
+        <v>58.77498286136166</v>
+      </c>
+      <c r="L3" s="4">
+        <v>38.68234396406748</v>
+      </c>
+      <c r="M3" s="5">
+        <v>129</v>
+      </c>
+      <c r="N3" s="5">
+        <v>6101212.398290634</v>
+      </c>
+      <c r="O3" s="4">
+        <v>161.2498982025698</v>
+      </c>
+      <c r="P3" s="5">
+        <v>37837</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>35.65891472868217</v>
+      </c>
+      <c r="C4" s="3">
+        <v>11.62790697674419</v>
+      </c>
+      <c r="D4" s="3">
+        <v>52.71317829457365</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.10077519379845</v>
+      </c>
+      <c r="F4" s="3">
+        <v>49.6124031007752</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.5592457599642684</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.3028179365032553</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.4660361542015118</v>
+      </c>
+      <c r="K4" s="4">
+        <v>65.75752781732879</v>
+      </c>
+      <c r="L4" s="4">
+        <v>59.84678216534004</v>
+      </c>
+      <c r="M4" s="5">
+        <v>129</v>
+      </c>
+      <c r="N4" s="5">
+        <v>3409641.594171524</v>
+      </c>
+      <c r="O4" s="4">
+        <v>109.7512342412053</v>
+      </c>
+      <c r="P4" s="5">
+        <v>31067</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>17.82945736434108</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>82.17054263565892</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>82.17054263565892</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.471472860969174</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.4163357078030526</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.3509103652963653</v>
+      </c>
+      <c r="K5" s="4">
+        <v>62.55866687760374</v>
+      </c>
+      <c r="L5" s="4">
+        <v>40.78308447357928</v>
+      </c>
+      <c r="M5" s="5">
+        <v>129</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4764663.021087646</v>
+      </c>
+      <c r="O5" s="4">
+        <v>136.304583507485</v>
+      </c>
+      <c r="P5" s="5">
+        <v>34956</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>11.62790697674419</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2.325581395348837</v>
+      </c>
+      <c r="D6" s="3">
+        <v>86.04651162790698</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.325581395348837</v>
+      </c>
+      <c r="F6" s="3">
+        <v>83.72093023255815</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.4394357693340276</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3424201837536457</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3318107960461465</v>
+      </c>
+      <c r="K6" s="4">
+        <v>62.39229024943333</v>
+      </c>
+      <c r="L6" s="4">
+        <v>47.03874234777888</v>
+      </c>
+      <c r="M6" s="5">
+        <v>129</v>
+      </c>
+      <c r="N6" s="5">
+        <v>3777457.894086838</v>
+      </c>
+      <c r="O6" s="4">
+        <v>101.4382205238282</v>
+      </c>
+      <c r="P6" s="5">
+        <v>37239</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>17.82945736434108</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="D7" s="3">
+        <v>81.3953488372093</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>81.3953488372093</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.4133799111815813</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3275331410876549</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3269871180109757</v>
+      </c>
+      <c r="K7" s="4">
+        <v>65.95686336550114</v>
+      </c>
+      <c r="L7" s="4">
+        <v>41.5761406794651</v>
+      </c>
+      <c r="M7" s="5">
+        <v>129</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3603115.580558777</v>
+      </c>
+      <c r="O7" s="4">
+        <v>126.3320213372174</v>
+      </c>
+      <c r="P7" s="5">
+        <v>28521</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>11.62790697674419</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6.2015503875969</v>
+      </c>
+      <c r="D8" s="3">
+        <v>82.17054263565892</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.325581395348837</v>
+      </c>
+      <c r="F8" s="3">
+        <v>79.84496124031007</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.465440713614357</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.403607935323457</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.379729631723778</v>
+      </c>
+      <c r="K8" s="4">
+        <v>58.02510151347357</v>
+      </c>
+      <c r="L8" s="4">
+        <v>42.93090890172238</v>
+      </c>
+      <c r="M8" s="5">
+        <v>129</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1989440.925359726</v>
+      </c>
+      <c r="O8" s="4">
+        <v>44.21078080312287</v>
+      </c>
+      <c r="P8" s="5">
+        <v>44999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>17.05426356589147</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3.875968992248062</v>
+      </c>
+      <c r="D9" s="3">
+        <v>79.06976744186046</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>79.06976744186046</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4698456032288307</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.4762736661220642</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4250148502752289</v>
+      </c>
+      <c r="K9" s="4">
+        <v>58.08363655539725</v>
+      </c>
+      <c r="L9" s="4">
+        <v>43.12227945129468</v>
+      </c>
+      <c r="M9" s="5">
+        <v>129</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2097360.929965973</v>
+      </c>
+      <c r="O9" s="4">
+        <v>60.63313954398465</v>
+      </c>
+      <c r="P9" s="5">
+        <v>34591</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>20.15503875968992</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1.550387596899225</v>
+      </c>
+      <c r="D10" s="3">
+        <v>78.29457364341084</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="F10" s="3">
+        <v>77.51937984496125</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.4650393744926455</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2193706712790097</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3243224389188559</v>
+      </c>
+      <c r="K10" s="4">
+        <v>65.87354321573606</v>
+      </c>
+      <c r="L10" s="4">
+        <v>44.23755267675989</v>
+      </c>
+      <c r="M10" s="5">
+        <v>129</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2704046.774864197</v>
+      </c>
+      <c r="O10" s="4">
+        <v>81.53806274656084</v>
+      </c>
+      <c r="P10" s="5">
+        <v>33163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>24.03100775193798</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.426356589147287</v>
+      </c>
+      <c r="D11" s="3">
+        <v>70.54263565891473</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.10077519379845</v>
+      </c>
+      <c r="F11" s="3">
+        <v>67.44186046511628</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.483826832457961</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.2518557408085285</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2756101641698409</v>
+      </c>
+      <c r="K11" s="4">
+        <v>64.06502135738026</v>
+      </c>
+      <c r="L11" s="4">
+        <v>44.9539566099576</v>
+      </c>
+      <c r="M11" s="5">
+        <v>129</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2302424.530982971</v>
+      </c>
+      <c r="O11" s="4">
+        <v>65.6335385114872</v>
+      </c>
+      <c r="P11" s="5">
+        <v>35080</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>18.6046511627907</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.325581395348837</v>
+      </c>
+      <c r="D12" s="3">
+        <v>79.06976744186046</v>
+      </c>
+      <c r="E12" s="3">
+        <v>2.325581395348837</v>
+      </c>
+      <c r="F12" s="3">
+        <v>76.74418604651163</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.4030081546039154</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.238936238769867</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.24306662881311</v>
+      </c>
+      <c r="K12" s="4">
+        <v>65.26578073089716</v>
+      </c>
+      <c r="L12" s="4">
+        <v>44.50505523472579</v>
+      </c>
+      <c r="M12" s="5">
+        <v>129</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1716708.913564682</v>
+      </c>
+      <c r="O12" s="4">
+        <v>53.75802948470852</v>
+      </c>
+      <c r="P12" s="5">
+        <v>31934</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>10.07751937984496</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.875968992248062</v>
+      </c>
+      <c r="D13" s="3">
+        <v>86.04651162790698</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.550387596899225</v>
+      </c>
+      <c r="F13" s="3">
+        <v>84.49612403100775</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.4096761980303567</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2768907641783285</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2911681488370062</v>
+      </c>
+      <c r="K13" s="4">
+        <v>60.15635711649022</v>
+      </c>
+      <c r="L13" s="4">
+        <v>37.92041690512103</v>
+      </c>
+      <c r="M13" s="5">
+        <v>129</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2979309.820890427</v>
+      </c>
+      <c r="O13" s="4">
+        <v>91.08532272128242</v>
+      </c>
+      <c r="P13" s="5">
+        <v>32709</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>13.95348837209302</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.550387596899225</v>
+      </c>
+      <c r="D14" s="3">
+        <v>84.49612403100775</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.550387596899225</v>
+      </c>
+      <c r="F14" s="3">
+        <v>82.17054263565892</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.9009443684996221</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.7197478642082591</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.6709325636183032</v>
+      </c>
+      <c r="K14" s="4">
+        <v>39.30338026683533</v>
+      </c>
+      <c r="L14" s="4">
+        <v>41.08249657492648</v>
+      </c>
+      <c r="M14" s="5">
+        <v>129</v>
+      </c>
+      <c r="N14" s="5">
+        <v>6222585.938215256</v>
+      </c>
+      <c r="O14" s="4">
+        <v>162.9333072769829</v>
+      </c>
+      <c r="P14" s="5">
+        <v>38191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>22.48062015503876</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>77.51937984496125</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>77.51937984496125</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.3597461655874856</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2785814835165725</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2806560649208096</v>
+      </c>
+      <c r="K15" s="4">
+        <v>66.56172546537967</v>
+      </c>
+      <c r="L15" s="4">
+        <v>42.20713455768852</v>
+      </c>
+      <c r="M15" s="5">
+        <v>129</v>
+      </c>
+      <c r="N15" s="5">
+        <v>4813383.99720192</v>
+      </c>
+      <c r="O15" s="4">
+        <v>158.2100971996424</v>
+      </c>
+      <c r="P15" s="5">
+        <v>30424</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>17.05426356589147</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1.550387596899225</v>
+      </c>
+      <c r="D16" s="3">
+        <v>81.3953488372093</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.875968992248062</v>
+      </c>
+      <c r="F16" s="3">
+        <v>76.74418604651163</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.8512257131302853</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.6635510957259325</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.7632533299853707</v>
+      </c>
+      <c r="K16" s="4">
+        <v>42.19928281390072</v>
+      </c>
+      <c r="L16" s="4">
+        <v>43.16320690910984</v>
+      </c>
+      <c r="M16" s="5">
+        <v>129</v>
+      </c>
+      <c r="N16" s="5">
+        <v>3741749.072313309</v>
+      </c>
+      <c r="O16" s="4">
+        <v>96.16667280868974</v>
+      </c>
+      <c r="P16" s="5">
+        <v>38909</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>21.70542635658915</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>78.29457364341084</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.7751937984496124</v>
+      </c>
+      <c r="F17" s="3">
+        <v>77.51937984496125</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.3905968597140232</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.2997412284494345</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2833659159778635</v>
+      </c>
+      <c r="K17" s="4">
+        <v>63.61282497495101</v>
+      </c>
+      <c r="L17" s="4">
+        <v>40.0089312037181</v>
+      </c>
+      <c r="M17" s="5">
+        <v>129</v>
+      </c>
+      <c r="N17" s="5">
+        <v>2916418.608427048</v>
+      </c>
+      <c r="O17" s="4">
+        <v>95.47941098140605</v>
+      </c>
+      <c r="P17" s="5">
+        <v>30545</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3215,7 +5383,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3253,13 +5421,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3341,13 +5509,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="M6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3426,16 +5594,16 @@
         <v>3</v>
       </c>
       <c r="K8" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="5">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="M8" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3517,13 +5685,13 @@
         <v>1</v>
       </c>
       <c r="L10" s="5">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3558,16 +5726,16 @@
         <v>0</v>
       </c>
       <c r="K11" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3602,16 +5770,16 @@
         <v>0</v>
       </c>
       <c r="K12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M12" s="5">
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3655,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3693,13 +5861,13 @@
         <v>0</v>
       </c>
       <c r="L14" s="5">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3778,16 +5946,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3825,13 +5993,13 @@
         <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3847,9 +6015,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>19</v>
+      </c>
+      <c r="C3" s="5">
+        <v>7</v>
+      </c>
+      <c r="D3" s="5">
+        <v>103</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>102</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>93</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5">
+        <v>15</v>
+      </c>
+      <c r="D4" s="5">
+        <v>68</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5">
+        <v>64</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>52</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>106</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>106</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>94</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5">
+        <v>111</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>108</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>3</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>92</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>105</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>105</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>90</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8</v>
+      </c>
+      <c r="D8" s="5">
+        <v>106</v>
+      </c>
+      <c r="E8" s="5">
+        <v>3</v>
+      </c>
+      <c r="F8" s="5">
+        <v>103</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>3</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>3</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5">
+        <v>91</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5">
+        <v>102</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>102</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>90</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>26</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>101</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>100</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>1</v>
+      </c>
+      <c r="L10" s="5">
+        <v>85</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>31</v>
+      </c>
+      <c r="C11" s="5">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>91</v>
+      </c>
+      <c r="E11" s="5">
+        <v>4</v>
+      </c>
+      <c r="F11" s="5">
+        <v>87</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>4</v>
+      </c>
+      <c r="I11" s="5">
+        <v>4</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>72</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>102</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3</v>
+      </c>
+      <c r="F12" s="5">
+        <v>99</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>3</v>
+      </c>
+      <c r="I12" s="5">
+        <v>3</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>86</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5">
+        <v>111</v>
+      </c>
+      <c r="E13" s="5">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>109</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5">
+        <v>2</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>93</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>109</v>
+      </c>
+      <c r="E14" s="5">
+        <v>2</v>
+      </c>
+      <c r="F14" s="5">
+        <v>106</v>
+      </c>
+      <c r="G14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5">
+        <v>2</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>98</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>29</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>100</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>100</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>87</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>22</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>105</v>
+      </c>
+      <c r="E16" s="5">
+        <v>5</v>
+      </c>
+      <c r="F16" s="5">
+        <v>99</v>
+      </c>
+      <c r="G16" s="5">
+        <v>1</v>
+      </c>
+      <c r="H16" s="5">
+        <v>5</v>
+      </c>
+      <c r="I16" s="5">
+        <v>5</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>87</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>28</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>101</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5">
+        <v>100</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>90</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6783,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6825,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,34 +6856,52 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5702242635826215</v>
+        <v>0.2591742824775747</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3061939225781245</v>
+        <v>0.3064913402964989</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4427432296516742</v>
+        <v>0.2427340765314141</v>
       </c>
       <c r="E3" s="4">
-        <v>61.04018351526659</v>
+        <v>62.51226071824065</v>
       </c>
       <c r="F3" s="4">
-        <v>40.58113521669019</v>
+        <v>43.17621351646648</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
         <v>34</v>
@@ -3960,10 +6915,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.09104683034369646</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2666922484491084</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3213740762818315</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6647656039634212</v>
@@ -4001,34 +6974,50 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>2</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6647656039634212</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3768324678296153</v>
+      </c>
+      <c r="R4" s="5">
+        <v>2</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2591742824775747</v>
+        <v>0.5702242635826215</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3064913402964989</v>
+        <v>0.3061939225781245</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2427340765314141</v>
+        <v>0.4427432296516742</v>
       </c>
       <c r="E5" s="4">
-        <v>62.51226071824065</v>
+        <v>61.04018351526659</v>
       </c>
       <c r="F5" s="4">
-        <v>43.17621351646648</v>
+        <v>40.58113521669019</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>34</v>
@@ -4042,9 +7031,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1162921170629829</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5616082943294086</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3034926317407241</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7062,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7081,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7123,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,51 +7154,87 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4657077105958161</v>
+        <v>0.2490517800827241</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4781216010595683</v>
+        <v>0.22088746307564</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4091325965546634</v>
+        <v>0.2477211709554981</v>
       </c>
       <c r="E3" s="4">
-        <v>67.79623477297876</v>
+        <v>69.44629014396432</v>
       </c>
       <c r="F3" s="4">
-        <v>62.15441444253776</v>
+        <v>66.15628739399611</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.07046936807202696</v>
+      </c>
+      <c r="O3" s="5">
+        <v>23</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2438875233373075</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2112325482907306</v>
+      </c>
+      <c r="R3" s="5">
+        <v>23</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>1.708467840335213</v>
@@ -4214,50 +7272,86 @@
       <c r="M4" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>1.335996719384772</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.9201041189060201</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4982123770410194</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2490517800827241</v>
+        <v>0.4657077105958161</v>
       </c>
       <c r="C5" s="4">
-        <v>0.22088746307564</v>
+        <v>0.4781216010595683</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2477211709554981</v>
+        <v>0.4091325965546634</v>
       </c>
       <c r="E5" s="4">
-        <v>69.44629014396432</v>
+        <v>67.79623477297876</v>
       </c>
       <c r="F5" s="4">
-        <v>66.15628739399611</v>
+        <v>62.15441444253776</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J5" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.415804130023107</v>
+      </c>
+      <c r="O5" s="5">
+        <v>15</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5137456376494778</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3390384968089857</v>
+      </c>
+      <c r="R5" s="5">
+        <v>15</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7362,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7381,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7423,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,51 +7454,87 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4758699973194734</v>
+        <v>0.2681403473637707</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3452338408396236</v>
+        <v>0.4207895632805267</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3608252114866491</v>
+        <v>0.2422696447228158</v>
       </c>
       <c r="E3" s="4">
-        <v>63.45198544534098</v>
+        <v>63.68612561303593</v>
       </c>
       <c r="F3" s="4">
-        <v>41.36673430102476</v>
+        <v>42.37786795692244</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
       </c>
       <c r="H3" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1311963637419402</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2953810816925583</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4479947542918187</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4154614978014958</v>
@@ -4427,50 +7572,86 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4009508426197418</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6426238061698536</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4439684196319901</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2681403473637707</v>
+        <v>0.4758699973194734</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4207895632805267</v>
+        <v>0.3452338408396236</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2422696447228158</v>
+        <v>0.3608252114866491</v>
       </c>
       <c r="E5" s="4">
-        <v>63.68612561303593</v>
+        <v>63.45198544534098</v>
       </c>
       <c r="F5" s="4">
-        <v>42.37786795692244</v>
+        <v>41.36673430102476</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.02337900220237321</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.47641369504511</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3485736982971055</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7662,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7681,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7723,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,25 +7754,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4305734965452672</v>
+        <v>0.2917304265251817</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4460895006530791</v>
+        <v>0.3743783530850891</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4276774312203891</v>
+        <v>0.2774500105806981</v>
       </c>
       <c r="E3" s="4">
-        <v>64.15757000474591</v>
+        <v>63.98591994937483</v>
       </c>
       <c r="F3" s="4">
-        <v>48.5796784766662</v>
+        <v>48.00062431715305</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
@@ -4585,24 +7799,42 @@
         <v>5</v>
       </c>
       <c r="I3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="5">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="5">
         <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1116287168785419</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2522260220612291</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3612794939703178</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5805832404873869</v>
@@ -4640,25 +7872,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.6590715114461643</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6732488348520087</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3079082267624952</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2917304265251817</v>
+        <v>0.4305734965452672</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3743783530850891</v>
+        <v>0.4460895006530791</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2774500105806981</v>
+        <v>0.4276774312203891</v>
       </c>
       <c r="E5" s="4">
-        <v>63.98591994937483</v>
+        <v>64.15757000474591</v>
       </c>
       <c r="F5" s="4">
-        <v>48.00062431715305</v>
+        <v>48.5796784766662</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
@@ -4667,23 +7917,41 @@
         <v>5</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1773501689035584</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.392832451088845</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3580728305281241</v>
+      </c>
+      <c r="R5" s="5">
+        <v>5</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7962,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7981,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8023,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,25 +8054,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3535903937888641</v>
+        <v>0.2164249186683414</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3612434383767694</v>
+        <v>0.3127423182151836</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3313820455719414</v>
+        <v>0.1874283236563034</v>
       </c>
       <c r="E3" s="4">
-        <v>66.55355165321932</v>
+        <v>67.22591362126248</v>
       </c>
       <c r="F3" s="4">
-        <v>42.50923469122357</v>
+        <v>42.43925914364529</v>
       </c>
       <c r="G3" s="5">
         <v>43</v>
@@ -4812,10 +8113,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1195007524212648</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2309847974629853</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3069294420019566</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.4636452682009853</v>
@@ -4853,25 +8172,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.6074989748970215</v>
+      </c>
+      <c r="O4" s="5">
+        <v>7</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6311255166869447</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3718652240640891</v>
+      </c>
+      <c r="R4" s="5">
+        <v>7</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2164249186683414</v>
+        <v>0.3535903937888641</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3127423182151836</v>
+        <v>0.3612434383767694</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1874283236563034</v>
+        <v>0.3313820455719414</v>
       </c>
       <c r="E5" s="4">
-        <v>67.22591362126248</v>
+        <v>66.55355165321932</v>
       </c>
       <c r="F5" s="4">
-        <v>42.43925914364529</v>
+        <v>42.50923469122357</v>
       </c>
       <c r="G5" s="5">
         <v>43</v>
@@ -4894,9 +8231,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1919874584045347</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3780294193948138</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3093462675689731</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8262,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5721147109115193</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3242602003402109</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4483244709959745</v>
-      </c>
-      <c r="E3" s="4">
-        <v>60.389969941465</v>
-      </c>
-      <c r="F3" s="4">
-        <v>45.90239841839654</v>
-      </c>
-      <c r="G3" s="5">
-        <v>43</v>
-      </c>
-      <c r="H3" s="5">
-        <v>7</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>36</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>35</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5547565316069867</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.8949635681421841</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4531663027832727</v>
-      </c>
-      <c r="E4" s="4">
-        <v>52.75905711121656</v>
-      </c>
-      <c r="F4" s="4">
-        <v>37.02148691535317</v>
-      </c>
-      <c r="G4" s="5">
-        <v>43</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="5">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5">
-        <v>36</v>
-      </c>
-      <c r="K4" s="5">
-        <v>1</v>
-      </c>
-      <c r="L4" s="5">
-        <v>35</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.292102739629906</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.3908821397642154</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.2890956717140729</v>
-      </c>
-      <c r="E5" s="4">
-        <v>60.92627748773928</v>
-      </c>
-      <c r="F5" s="4">
-        <v>45.86884137141673</v>
-      </c>
-      <c r="G5" s="5">
-        <v>43</v>
-      </c>
-      <c r="H5" s="5">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5">
-        <v>3</v>
-      </c>
-      <c r="J5" s="5">
-        <v>34</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>33</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4410084259152415</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.4882703869118896</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4444978815921085</v>
-      </c>
-      <c r="E3" s="4">
-        <v>60.96899224806192</v>
-      </c>
-      <c r="F3" s="4">
-        <v>46.05665678164555</v>
-      </c>
-      <c r="G3" s="5">
-        <v>43</v>
-      </c>
-      <c r="H3" s="5">
-        <v>9</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>34</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>34</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7782171289934602</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.9780721101025358</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6889103028071557</v>
-      </c>
-      <c r="E4" s="4">
-        <v>52.3959816484734</v>
-      </c>
-      <c r="F4" s="4">
-        <v>37.2321939545289</v>
-      </c>
-      <c r="G4" s="5">
-        <v>43</v>
-      </c>
-      <c r="H4" s="5">
-        <v>4</v>
-      </c>
-      <c r="I4" s="5">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5">
-        <v>34</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>34</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.339294041953577</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.430256443639323</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3440092019272478</v>
-      </c>
-      <c r="E5" s="4">
-        <v>60.88593576965651</v>
-      </c>
-      <c r="F5" s="4">
-        <v>46.0779876177103</v>
-      </c>
-      <c r="G5" s="5">
-        <v>43</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>34</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>34</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/ZhaoTrends2019.xlsx
+++ b/public/downloads/ZhaoTrends2019.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1450406291715316</v>
+        <v>0.2137522662443621</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2794777826185646</v>
+        <v>0.2948834860673299</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3425352633737049</v>
+        <v>0.3336001750697237</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -1673,16 +1673,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.06084108905621864</v>
+        <v>0.2646123765478983</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5620878266175199</v>
+        <v>0.5674169037151122</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3155686161893225</v>
+        <v>0.2864584322619397</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -1855,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.188366275010848</v>
+        <v>0.1567132796874944</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2550584957226067</v>
+        <v>0.2641082620589593</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3881023212186598</v>
+        <v>0.3845853217382873</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -1971,16 +1971,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3169623921071971</v>
+        <v>0.3747056525976689</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3762611849704252</v>
+        <v>0.3786808080341593</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.341423480367481</v>
+        <v>0.3244351415408018</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -2153,16 +2153,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1433422166278205</v>
+        <v>0.1309181524368626</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.265876745256695</v>
+        <v>0.2603870424746438</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2726549939204798</v>
+        <v>0.2712745423437066</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -2212,16 +2212,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4321524507079449</v>
+        <v>0.3828935846227353</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6391539010962983</v>
+        <v>0.6014180221778589</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1266158835306562</v>
+        <v>0.1146636404242319</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -2271,16 +2271,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2417865930804247</v>
+        <v>0.3381245558341277</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4900874771249432</v>
+        <v>0.5306398121343577</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2485350488582984</v>
+        <v>0.2152809210600584</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -2453,16 +2453,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.04631235105259433</v>
+        <v>-0.005433137836911572</v>
       </c>
       <c r="O3" s="5">
         <v>14</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2259408207373873</v>
+        <v>0.2277410481913132</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2210198118478979</v>
+        <v>0.2127604994531284</v>
       </c>
       <c r="R3" s="5">
         <v>14</v>
@@ -2512,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3920189298486487</v>
+        <v>0.3547866290869239</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7101069127993289</v>
+        <v>0.6929100437881509</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2442850955143073</v>
@@ -2571,16 +2571,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.05533725346857198</v>
+        <v>0.1956644257128914</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.515432763837167</v>
+        <v>0.5296215453819962</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2952309114643608</v>
+        <v>0.2714487246590928</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -2753,13 +2753,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.007506069033812679</v>
+        <v>0.01527235162537011</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2029826499919381</v>
+        <v>0.1980405663858104</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2440251503466833</v>
@@ -2812,16 +2812,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.264519301921657</v>
+        <v>0.1615930610650764</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6573473334014234</v>
+        <v>0.5859102686541628</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2471088495615334</v>
+        <v>0.2324051008677361</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -2871,16 +2871,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.01602553771226035</v>
+        <v>-0.000138316575942099</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3486944804183846</v>
+        <v>0.3513258055350688</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2280562867525121</v>
+        <v>0.2262603029427118</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -3053,13 +3053,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3109015127577782</v>
+        <v>-0.3193557243756118</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2554718453357407</v>
+        <v>0.2592074272133881</v>
       </c>
       <c r="Q3" s="4">
         <v>0.2580370198730459</v>
@@ -3349,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4025804568760946</v>
+        <v>-0.8047642610979722</v>
       </c>
       <c r="O3" s="5">
         <v>7</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6266590708685068</v>
+        <v>0.5506186647518801</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6273793087082586</v>
+        <v>0.5699244795337047</v>
       </c>
       <c r="R3" s="5">
         <v>7</v>
@@ -3408,16 +3408,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.03839443161191663</v>
+        <v>0.2859965356075236</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>1.181007702715642</v>
+        <v>1.319152460118268</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.847311853318783</v>
+        <v>0.8119401241765535</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -3467,16 +3467,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.464623612093163</v>
+        <v>-1.894155474969352</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8951663319147173</v>
+        <v>0.9273381373422057</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6581558553898433</v>
+        <v>0.4433899239517487</v>
       </c>
       <c r="R5" s="5">
         <v>4</v>
@@ -3649,16 +3649,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2453656339305791</v>
+        <v>-0.3036568660868042</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2204809633128243</v>
+        <v>0.2005499424232045</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2541752771055424</v>
+        <v>0.2513227121762501</v>
       </c>
       <c r="R3" s="5">
         <v>10</v>
@@ -3708,16 +3708,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1272178452830015</v>
+        <v>-0.2258924728876934</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4696097253795317</v>
+        <v>0.4034786715710542</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2373842666880218</v>
+        <v>0.2052266502060804</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1068164233666424</v>
+        <v>-0.09550790178191448</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.389147808070101</v>
+        <v>0.39313001864157</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3400651850732983</v>
@@ -3949,16 +3949,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.232779971657087</v>
+        <v>-0.6895958449497357</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6054024404024686</v>
+        <v>0.5135565310277277</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7540656873200703</v>
+        <v>0.7033083680653315</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -4008,16 +4008,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1282149714834951</v>
+        <v>-0.04572335716653697</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>1.127787548235959</v>
+        <v>1.040178131496704</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6843698272397872</v>
+        <v>0.6700573249726255</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -4067,16 +4067,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>-1.485050212914359</v>
+        <v>-1.804520461098122</v>
       </c>
       <c r="O5" s="5">
         <v>6</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8204871507524281</v>
+        <v>0.8232073377621425</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4673148604343169</v>
+        <v>0.3596740206156426</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -4249,13 +4249,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1050346411140037</v>
+        <v>-0.0769300108635349</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2198017569366305</v>
+        <v>0.2243896202595671</v>
       </c>
       <c r="Q3" s="4">
         <v>0.3025212138836768</v>
@@ -4308,16 +4308,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1797096455886912</v>
+        <v>0.01136074600154302</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.605475944604511</v>
+        <v>0.4788917113280811</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3329217843935517</v>
+        <v>0.2898230801618294</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4367,16 +4367,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1470072226634819</v>
+        <v>-0.1177571753901958</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3465128776009282</v>
+        <v>0.3481641207950317</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2634717998006036</v>
+        <v>0.2602217945480163</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4513,13 +4513,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.4976887155806461</v>
+        <v>0.4964925706286137</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3196827724274477</v>
+        <v>0.310234023388934</v>
       </c>
       <c r="J3" s="4">
-        <v>0.4010734255587064</v>
+        <v>0.4036560935296878</v>
       </c>
       <c r="K3" s="4">
         <v>58.77498286136166</v>
@@ -4563,13 +4563,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.5592457599642684</v>
+        <v>0.538791138832572</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3028179365032553</v>
+        <v>0.2972670801501489</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4660361542015118</v>
+        <v>0.4479270812012295</v>
       </c>
       <c r="K4" s="4">
         <v>65.75752781732879</v>
@@ -4613,13 +4613,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.471472860969174</v>
+        <v>0.4023462423510625</v>
       </c>
       <c r="I5" s="4">
-        <v>0.4163357078030526</v>
+        <v>0.3839794386648429</v>
       </c>
       <c r="J5" s="4">
-        <v>0.3509103652963653</v>
+        <v>0.2797315614924609</v>
       </c>
       <c r="K5" s="4">
         <v>62.55866687760374</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4394357693340276</v>
+        <v>0.4101378676769891</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3424201837536457</v>
+        <v>0.3196216220442716</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3318107960461465</v>
+        <v>0.2929568228418697</v>
       </c>
       <c r="K6" s="4">
         <v>62.39229024943333</v>
@@ -4713,13 +4713,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.4133799111815813</v>
+        <v>0.3402795028038707</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3275331410876549</v>
+        <v>0.3104994908619235</v>
       </c>
       <c r="J7" s="4">
-        <v>0.3269871180109757</v>
+        <v>0.2516200001345236</v>
       </c>
       <c r="K7" s="4">
         <v>65.95686336550114</v>
@@ -4763,13 +4763,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.465440713614357</v>
+        <v>0.4723523071298096</v>
       </c>
       <c r="I8" s="4">
-        <v>0.403607935323457</v>
+        <v>0.3864491475024193</v>
       </c>
       <c r="J8" s="4">
-        <v>0.379729631723778</v>
+        <v>0.3811617611834899</v>
       </c>
       <c r="K8" s="4">
         <v>58.02510151347357</v>
@@ -4813,13 +4813,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4698456032288307</v>
+        <v>0.4736687330288596</v>
       </c>
       <c r="I9" s="4">
-        <v>0.4762736661220642</v>
+        <v>0.4678851186328157</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4250148502752289</v>
+        <v>0.4278348089952702</v>
       </c>
       <c r="K9" s="4">
         <v>58.08363655539725</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4650393744926455</v>
+        <v>0.4641482922622868</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2193706712790097</v>
+        <v>0.2037041651549131</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3243224389188559</v>
+        <v>0.3223397562945073</v>
       </c>
       <c r="K10" s="4">
         <v>65.87354321573606</v>
@@ -4913,13 +4913,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.483826832457961</v>
+        <v>0.4834242124538201</v>
       </c>
       <c r="I11" s="4">
-        <v>0.2518557408085285</v>
+        <v>0.2396868882799891</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2756101641698409</v>
+        <v>0.2684466036081508</v>
       </c>
       <c r="K11" s="4">
         <v>64.06502135738026</v>
@@ -4963,13 +4963,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.4030081546039154</v>
+        <v>0.3784255468583474</v>
       </c>
       <c r="I12" s="4">
-        <v>0.238936238769867</v>
+        <v>0.2339741514721677</v>
       </c>
       <c r="J12" s="4">
-        <v>0.24306662881311</v>
+        <v>0.2215449506318151</v>
       </c>
       <c r="K12" s="4">
         <v>65.26578073089716</v>
@@ -5013,13 +5013,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.4096761980303567</v>
+        <v>0.4109213919895724</v>
       </c>
       <c r="I13" s="4">
         <v>0.2768907641783285</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2911681488370062</v>
+        <v>0.2925444158445605</v>
       </c>
       <c r="K13" s="4">
         <v>60.15635711649022</v>
@@ -5063,13 +5063,13 @@
         <v>0.7751937984496124</v>
       </c>
       <c r="H14" s="4">
-        <v>0.9009443684996221</v>
+        <v>0.9323697540707847</v>
       </c>
       <c r="I14" s="4">
-        <v>0.7197478642082591</v>
+        <v>0.6359228845432668</v>
       </c>
       <c r="J14" s="4">
-        <v>0.6709325636183032</v>
+        <v>0.7113110003234383</v>
       </c>
       <c r="K14" s="4">
         <v>39.30338026683533</v>
@@ -5113,13 +5113,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.3597461655874856</v>
+        <v>0.3323862108786095</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2785814835165725</v>
+        <v>0.2676178904948348</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2806560649208096</v>
+        <v>0.2441329920710161</v>
       </c>
       <c r="K15" s="4">
         <v>66.56172546537967</v>
@@ -5163,13 +5163,13 @@
         <v>0.7751937984496124</v>
       </c>
       <c r="H16" s="4">
-        <v>0.8512257131302853</v>
+        <v>0.7923140000955248</v>
       </c>
       <c r="I16" s="4">
-        <v>0.6635510957259325</v>
+        <v>0.6131183643385092</v>
       </c>
       <c r="J16" s="4">
-        <v>0.7632533299853707</v>
+        <v>0.6731390212579922</v>
       </c>
       <c r="K16" s="4">
         <v>42.19928281390072</v>
@@ -5213,13 +5213,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3905968597140232</v>
+        <v>0.3504818174608933</v>
       </c>
       <c r="I17" s="4">
-        <v>0.2997412284494345</v>
+        <v>0.284843428972335</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2833659159778635</v>
+        <v>0.242535782126248</v>
       </c>
       <c r="K17" s="4">
         <v>63.61282497495101</v>
@@ -6916,16 +6916,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.09104683034369646</v>
+        <v>-0.04558160786376675</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2666922484491084</v>
+        <v>0.2611138438335753</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3213740762818315</v>
+        <v>0.3014267172005248</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -7032,13 +7032,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1162921170629829</v>
+        <v>0.08776921717773689</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5616082943294086</v>
+        <v>0.5635982640888444</v>
       </c>
       <c r="Q5" s="4">
         <v>0.3034926317407241</v>
@@ -7214,16 +7214,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.07046936807202696</v>
+        <v>0.05512448773436063</v>
       </c>
       <c r="O3" s="5">
         <v>23</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2438875233373075</v>
+        <v>0.2435306656550362</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2112325482907306</v>
+        <v>0.2105653795803973</v>
       </c>
       <c r="R3" s="5">
         <v>23</v>
@@ -7273,13 +7273,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>1.335996719384772</v>
+        <v>1.32666260861329</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.9201041189060201</v>
+        <v>0.9194529018754516</v>
       </c>
       <c r="Q4" s="4">
         <v>0.4982123770410194</v>
@@ -7332,16 +7332,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.415804130023107</v>
+        <v>0.2438921930859408</v>
       </c>
       <c r="O5" s="5">
         <v>15</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5137456376494778</v>
+        <v>0.4533898489672284</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3390384968089857</v>
+        <v>0.3230388626819704</v>
       </c>
       <c r="R5" s="5">
         <v>15</v>
@@ -7514,16 +7514,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1311963637419402</v>
+        <v>-0.0009653170676955369</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2953810816925583</v>
+        <v>0.2680729996613733</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4479947542918187</v>
+        <v>0.4207895632805267</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -7573,16 +7573,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4009508426197418</v>
+        <v>0.1313624596446914</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6426238061698536</v>
+        <v>0.4634525558148792</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4439684196319901</v>
+        <v>0.3829896505123703</v>
       </c>
       <c r="R4" s="5">
         <v>8</v>
@@ -7632,16 +7632,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.02337900220237321</v>
+        <v>-0.01534350692915609</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.47641369504511</v>
+        <v>0.475513171576935</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3485736982971055</v>
+        <v>0.3430419112783156</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -7814,16 +7814,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1116287168785419</v>
+        <v>0.08856150622619907</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2522260220612291</v>
+        <v>0.2565683431963127</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3612794939703178</v>
+        <v>0.3566660518398493</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7873,16 +7873,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6590715114461643</v>
+        <v>0.4955572039617948</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6732488348520087</v>
+        <v>0.5600867035969241</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3079082267624952</v>
+        <v>0.2752053652656213</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1773501689035584</v>
+        <v>0.3327470764074576</v>
       </c>
       <c r="O5" s="5">
         <v>5</v>
       </c>
       <c r="P5" s="4">
-        <v>0.392832451088845</v>
+        <v>0.4137585562377305</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3580728305281241</v>
+        <v>0.3269934490273442</v>
       </c>
       <c r="R5" s="5">
         <v>5</v>
@@ -8114,13 +8114,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1195007524212648</v>
+        <v>0.1616655053216647</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2309847974629853</v>
+        <v>0.244052469987289</v>
       </c>
       <c r="Q3" s="4">
         <v>0.3069294420019566</v>
@@ -8173,16 +8173,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6074989748970215</v>
+        <v>0.3082808405889921</v>
       </c>
       <c r="O4" s="5">
         <v>7</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6311255166869447</v>
+        <v>0.4217634097719787</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3718652240640891</v>
+        <v>0.3291197763057991</v>
       </c>
       <c r="R4" s="5">
         <v>7</v>
@@ -8232,16 +8232,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1919874584045347</v>
+        <v>0.1231710383142115</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3780294193948138</v>
+        <v>0.3550226286523446</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3093462675689731</v>
+        <v>0.2977767899584992</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
